--- a/projects/demo/login_cases.xlsx
+++ b/projects/demo/login_cases.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>tags</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>timeout_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,7 +477,6 @@
           <t>go</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>https://the-internet.herokuapp.com/login</t>
@@ -482,6 +486,9 @@
         <is>
           <t>smoke</t>
         </is>
+      </c>
+      <c r="H2" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="3">
@@ -578,7 +585,6 @@
           <t>button[type="submit"]</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>smoke</t>
@@ -604,7 +610,6 @@
           <t>assert_text</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Welcome to the Secure Area</t>
